--- a/docs/workbook-split/dateien/Fremdleistungen.xlsx
+++ b/docs/workbook-split/dateien/Fremdleistungen.xlsx
@@ -659,9 +659,8 @@
       <c r="E7" s="6" t="n">
         <v>5487599</v>
       </c>
-      <c r="F7" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E7/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F7" s="7" t="n">
+        <v>0.6263693842788743</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -690,9 +689,8 @@
       <c r="E8" s="6" t="n">
         <v>709679</v>
       </c>
-      <c r="F8" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E8/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F8" s="7" t="n">
+        <v>0.08100467950840563</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -721,9 +719,8 @@
       <c r="E9" s="6" t="n">
         <v>634905</v>
       </c>
-      <c r="F9" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E9/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F9" s="7" t="n">
+        <v>0.07246977301467887</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -752,9 +749,8 @@
       <c r="E10" s="6" t="n">
         <v>582847</v>
       </c>
-      <c r="F10" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E10/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F10" s="7" t="n">
+        <v>0.06652773216825593</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -783,9 +779,8 @@
       <c r="E11" s="6" t="n">
         <v>487891</v>
       </c>
-      <c r="F11" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E11/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F11" s="7" t="n">
+        <v>0.0556891976372917</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -814,9 +809,8 @@
       <c r="E12" s="6" t="n">
         <v>343263</v>
       </c>
-      <c r="F12" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E12/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F12" s="7" t="n">
+        <v>0.03918096674988811</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -845,9 +839,8 @@
       <c r="E13" s="6" t="n">
         <v>255298</v>
       </c>
-      <c r="F13" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E13/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F13" s="7" t="n">
+        <v>0.02914040385742983</v>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
@@ -876,9 +869,8 @@
       <c r="E14" s="6" t="n">
         <v>163751</v>
       </c>
-      <c r="F14" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E14/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F14" s="7" t="n">
+        <v>0.01869098180188639</v>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
@@ -907,9 +899,8 @@
       <c r="E15" s="6" t="n">
         <v>78591</v>
       </c>
-      <c r="F15" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E15/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F15" s="7" t="n">
+        <v>0.008970589192078542</v>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
@@ -938,9 +929,8 @@
       <c r="E16" s="6" t="n">
         <v>17139</v>
       </c>
-      <c r="F16" s="7">
-        <f>IF(SUM($E$7:$E$16)=0,"n.a.",E16/SUM($E$7:$E$16))</f>
-        <v/>
+      <c r="F16" s="7" t="n">
+        <v>0.001956291791210624</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1809,6 +1799,8 @@
       <c r="M60" s="1" t="n"/>
       <c r="N60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
